--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY535"/>
+  <dimension ref="A1:AZ535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492249</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004817</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859669</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111689384</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859668</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1721,6 +1771,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859675</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126479192</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1928,6 +1988,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523335</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2029,6 +2094,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492310</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398377</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230845</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230878</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2433,6 +2518,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192906</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2534,6 +2624,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492285</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126419167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2744,6 +2844,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679673</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2849,6 +2954,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230833</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2951,6 +3061,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126004559</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3053,6 +3168,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94160642</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3155,6 +3275,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126419146</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3262,6 +3387,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859672</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3363,6 +3493,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624959</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3464,6 +3599,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129625082</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3565,6 +3705,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968158</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3666,6 +3811,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398178</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3771,6 +3921,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624864</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3878,6 +4033,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133768363</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3984,6 +4144,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592510</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4090,6 +4255,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592546</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4191,6 +4361,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626517</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4292,6 +4467,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319637</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4393,6 +4573,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647001</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4494,6 +4679,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968206</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4595,6 +4785,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887003</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4696,6 +4891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319589</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4797,6 +4997,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319624</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4898,6 +5103,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319794</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4999,6 +5209,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646956</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5100,6 +5315,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128315320</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5201,6 +5421,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128398188</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5302,6 +5527,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192837</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5403,6 +5633,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982712</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5508,6 +5743,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120047138</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5618,6 +5858,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626241</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5719,6 +5964,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132642750</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5820,6 +6070,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646946</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5921,6 +6176,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646987</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6027,6 +6287,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319612</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6128,6 +6393,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646965</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6242,6 +6512,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94160520</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6347,6 +6622,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123017501</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6452,6 +6732,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932304</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6557,6 +6842,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968176</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6662,6 +6952,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96994112</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6764,6 +7059,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523271</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6866,6 +7166,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005083</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6972,6 +7277,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488433</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7079,6 +7389,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94160608</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7190,6 +7505,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488188</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7291,6 +7611,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319393</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7397,6 +7722,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319573</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7498,6 +7828,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679602</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7599,6 +7934,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679586</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7704,6 +8044,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679857</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7814,6 +8159,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478596</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7915,6 +8265,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814084</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8016,6 +8371,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526460</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8117,6 +8477,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526442</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8222,6 +8587,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456417</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8324,6 +8694,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134181062</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8426,6 +8801,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90118545</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8528,6 +8908,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90118484</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8629,6 +9014,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661386</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8730,6 +9120,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319250</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8831,6 +9226,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319271</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8932,6 +9332,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112318834</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9033,6 +9438,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967646</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9134,6 +9544,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967861</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9235,6 +9650,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967977</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9336,6 +9756,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319935</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9437,6 +9862,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112525025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9538,6 +9968,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128969381</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9639,6 +10074,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526502</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9740,6 +10180,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967829</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9841,6 +10286,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968120</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9942,6 +10392,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855390</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10043,6 +10498,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235546</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10149,6 +10609,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122202986</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10255,6 +10720,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526610</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10361,6 +10831,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128967940</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10462,6 +10937,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97593418</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10563,6 +11043,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519668</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10664,6 +11149,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112524822</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10765,6 +11255,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526637</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10866,6 +11361,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120047194</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10967,6 +11467,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317802</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11068,6 +11573,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526527</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11169,6 +11679,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526648</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11283,6 +11798,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370613</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11397,6 +11917,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370709</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11502,6 +12027,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626541</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11607,6 +12137,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132275274</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11714,6 +12249,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132458590</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11817,6 +12357,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99954993</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11918,6 +12463,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112384373</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12033,6 +12583,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102043433</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12148,6 +12703,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121108956</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12249,6 +12809,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855333</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12350,6 +12915,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661321</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12451,6 +13021,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646883</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12552,6 +13127,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982741</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12653,6 +13233,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235541</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12767,6 +13352,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131833708</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12868,6 +13458,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121109277</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12969,6 +13564,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646940</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13070,6 +13670,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647386</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13171,6 +13776,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647410</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13272,6 +13882,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679529</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13373,6 +13988,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679533</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13474,6 +14094,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128679541</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13579,6 +14204,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96993976</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13680,6 +14310,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103529463</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13785,6 +14420,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527028</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13896,6 +14536,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87803738</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13997,6 +14642,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102316141</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14102,6 +14752,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317810</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14207,6 +14862,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131056554</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14316,6 +14976,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132643103</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14423,6 +15088,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661363</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14532,6 +15202,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647243</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14633,6 +15308,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319548</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14734,6 +15414,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647116</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14835,6 +15520,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647280</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14937,6 +15627,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102043494</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15038,6 +15733,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722827</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15148,6 +15848,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202351</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15258,6 +15963,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202408</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15359,6 +16069,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119061058</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15464,6 +16179,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132813421</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15567,6 +16287,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120026935</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15669,6 +16394,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97085747</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15771,6 +16501,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100909866</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15881,6 +16616,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478559</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15991,6 +16731,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478679</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16097,6 +16842,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232695</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16198,6 +16948,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661786</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16304,6 +17059,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661806</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16410,6 +17170,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661894</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16511,6 +17276,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814103</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16612,6 +17382,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371177</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16717,6 +17492,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130955531</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16822,6 +17602,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130955545</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16927,6 +17712,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135387324</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17033,6 +17823,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112690902</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17134,6 +17929,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840826</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17235,6 +18035,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840859</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17336,6 +18141,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840879</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17437,6 +18247,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840908</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17543,6 +18358,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97593519</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17649,6 +18469,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232601</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17755,6 +18580,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232654</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17861,6 +18691,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232666</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17962,6 +18797,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660814</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18063,6 +18903,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660860</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18164,6 +19009,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660933</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18265,6 +19115,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661005</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18366,6 +19221,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661016</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18467,6 +19327,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661075</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18573,6 +19438,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661135</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18679,6 +19549,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661220</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18785,6 +19660,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661654</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18886,6 +19766,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492871</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18987,6 +19872,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814101</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19093,6 +19983,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647614</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19198,6 +20093,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492905</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19299,6 +20199,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112524787</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19400,6 +20305,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112814098</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19506,6 +20416,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983687</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19607,6 +20522,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128984152</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19708,6 +20628,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492783</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19814,6 +20739,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660980</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19915,6 +20845,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492986</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20016,6 +20951,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647680</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20117,6 +21057,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112525059</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20218,6 +21163,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983919</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20319,6 +21269,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983928</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20420,6 +21375,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983948</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20521,6 +21481,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983913</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20627,6 +21592,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661177</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20728,6 +21698,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661427</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20834,6 +21809,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371122</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20935,6 +21915,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128984305</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21036,6 +22021,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513514</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21137,6 +22127,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370534</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21238,6 +22233,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370805</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21339,6 +22339,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128370831</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21445,6 +22450,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371143</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21546,6 +22556,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371163</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21647,6 +22662,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526712</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21748,6 +22768,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983981</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21862,6 +22887,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128371011</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21967,6 +22997,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526827</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22068,6 +23103,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983940</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22182,6 +23222,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779299</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22296,6 +23341,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779314</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22402,6 +23452,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983888</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22504,6 +23559,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235377</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22605,6 +23665,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89855305</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22706,6 +23771,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235394</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22812,6 +23882,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115861916</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22913,6 +23988,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129660798</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23014,6 +24094,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661257</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23120,6 +24205,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235411</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23221,6 +24311,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492389</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23322,6 +24417,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112857689</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23423,6 +24523,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730264</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23524,6 +24629,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730329</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23625,6 +24735,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730403</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23726,6 +24841,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112730504</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23827,6 +24947,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135387419</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23928,6 +25053,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492758</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24029,6 +25159,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112562146</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24130,6 +25265,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97235532</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24231,6 +25371,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647360</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24332,6 +25477,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527017</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24442,6 +25592,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118914003</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24543,6 +25698,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647342</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24644,6 +25804,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112562168</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24751,6 +25916,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127456360</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24865,6 +26035,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779328</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -24970,6 +26145,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107569089</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25071,6 +26251,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122189878</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25176,6 +26361,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526994</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25281,6 +26471,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132275253</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25387,6 +26582,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128554024</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25488,6 +26688,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128984320</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25594,6 +26799,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180726</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25700,6 +26910,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892267</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25801,6 +27016,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112562025</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25902,6 +27122,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112562008</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26007,6 +27232,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132429104</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26114,6 +27344,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94241756</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26224,6 +27459,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202449</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26334,6 +27574,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202482</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26444,6 +27689,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202512</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26554,6 +27804,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202558</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26664,6 +27919,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202609</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26779,6 +28039,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847807</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26894,6 +28159,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847819</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27011,6 +28281,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16088616</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27112,6 +28387,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847793</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27218,6 +28498,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833089</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27319,6 +28604,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128847959</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27420,6 +28710,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848222</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27521,6 +28816,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134928880</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27622,6 +28922,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848236</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27723,6 +29028,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128834159</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27828,6 +29138,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126769372</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27930,6 +29245,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98528826</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28032,6 +29352,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122757472</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28134,6 +29459,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132813106</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28235,6 +29565,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670485</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28341,6 +29676,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96994383</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28447,6 +29787,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670528</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -28549,6 +29894,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101544076</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -28647,6 +29997,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96288806</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -28748,6 +30103,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840893</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28854,6 +30214,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661065</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -28955,6 +30320,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983095</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29056,6 +30426,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006121</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29157,6 +30532,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983204</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29258,6 +30638,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983483</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29359,6 +30744,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678462</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29468,6 +30858,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105320486</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -29578,6 +30973,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95082357</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -29683,6 +31083,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128983066</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -29788,6 +31193,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129661923</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -29893,6 +31303,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670477</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -29998,6 +31413,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88399805</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -30113,6 +31533,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94423474</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -30220,6 +31645,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100755746</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -30344,6 +31774,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101618014</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -30455,6 +31890,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116802088</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -30566,6 +32006,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109662437</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -30685,6 +32130,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125864996</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -30795,6 +32245,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478968</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -30905,6 +32360,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100478990</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31020,6 +32480,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118723451</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -31135,6 +32600,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030245</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -31236,6 +32706,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670329</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -31337,6 +32812,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513167</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -31442,6 +32922,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670120</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -31547,6 +33032,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678484</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -31652,6 +33142,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030423</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -31763,6 +33258,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116802070</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -31865,6 +33365,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116976780</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -31975,6 +33480,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88925996</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32086,6 +33596,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94682766</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -32209,6 +33724,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000763</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -32311,6 +33831,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100670159</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -32413,6 +33938,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103529403</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -32527,6 +34057,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117979016</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -32646,6 +34181,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000774</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -32757,6 +34297,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133030065</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -32855,6 +34400,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88926061</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -32953,6 +34503,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92648384</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -33060,6 +34615,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92648637</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -33167,6 +34727,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92648716</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -33274,6 +34839,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92648757</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -33376,6 +34946,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92648837</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -33478,6 +35053,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100669907</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -33579,6 +35159,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135419</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -33686,6 +35271,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126753155</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -33788,6 +35378,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116976725</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -33899,6 +35494,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94682718</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -34000,6 +35600,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892429</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -34101,6 +35706,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892441</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -34202,6 +35812,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123708052</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -34303,6 +35918,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892378</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -34404,6 +36024,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892455</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -34510,6 +36135,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892467</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -34611,6 +36241,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892491</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -34717,6 +36352,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892512</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -34822,6 +36462,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946786</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -34923,6 +36568,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120489125</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -35024,6 +36674,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848318</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -35125,6 +36780,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848323</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -35226,6 +36886,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128848447</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -35332,6 +36997,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892461</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -35433,6 +37103,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946710</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -35534,6 +37209,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112947009</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -35641,6 +37321,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107227361</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -35750,6 +37435,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87739942</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -35864,6 +37554,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117246443</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -35965,6 +37660,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120027032</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -36066,6 +37766,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279963</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -36167,6 +37872,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892128</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -36273,6 +37983,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892157</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -36379,6 +38094,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892527</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -36480,6 +38200,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128849972</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -36581,6 +38306,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128849336</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -36703,6 +38433,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929749</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -36808,6 +38543,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122757537</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -36913,6 +38653,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131936863</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -37020,6 +38765,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117246388</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -37122,6 +38872,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122757487</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -37232,6 +38987,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202640</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -37342,6 +39102,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202663</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -37452,6 +39217,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108513325</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -37562,6 +39332,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564429</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -37677,6 +39452,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929407</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -37778,6 +39558,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128850746</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -37879,6 +39664,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122833929</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -37987,6 +39777,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71736134</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -38096,6 +39891,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564460</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -38201,6 +40001,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129892543</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -38311,6 +40116,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954667</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -38418,6 +40228,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116251522</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -38525,6 +40340,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131936564</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -38626,6 +40446,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006066</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -38741,6 +40566,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122552695</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -38856,6 +40686,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134860</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -38957,6 +40792,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129669898</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -39058,6 +40898,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670041</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -39159,6 +41004,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670433</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -39260,6 +41110,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670436</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -39366,6 +41221,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134940</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -39467,6 +41327,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006200</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -39577,6 +41442,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100755754</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -39678,6 +41548,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135016</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -39788,6 +41663,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100699954</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -39889,6 +41769,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006188</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -39990,6 +41875,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134736</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -40096,6 +41986,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670440</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -40197,6 +42092,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006096</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -40298,6 +42198,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129134778</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -40399,6 +42304,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513064</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -40504,6 +42414,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513094</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -40605,6 +42520,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006083</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -40714,6 +42634,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94210590</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -40828,6 +42753,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94210587</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -40929,6 +42859,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129006215</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -41038,6 +42973,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104945560</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -41145,6 +43085,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118723580</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -41261,6 +43206,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103235580</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -41373,6 +43323,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135387367</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -41479,6 +43434,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93618565</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -41581,6 +43541,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110144437</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -41688,6 +43653,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180219</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -41790,6 +43760,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029560</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -41900,6 +43875,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670447</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -42001,6 +43981,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670421</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -42107,6 +44092,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670690</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -42208,6 +44198,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112077770</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -42309,6 +44304,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120513107</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -42414,6 +44414,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129670413</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -42519,6 +44524,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121407708</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -42620,6 +44630,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175622</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -42721,6 +44736,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175630</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -42822,6 +44842,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946872</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -42923,6 +44948,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175200</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -43024,6 +45054,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946869</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -43125,6 +45160,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120026988</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -43226,6 +45266,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129102373</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -43336,6 +45381,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100884203</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -43437,6 +45487,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111483229</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -43538,6 +45593,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687092</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -43639,6 +45699,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687119</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -43759,6 +45824,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103235895</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -43871,6 +45941,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128876899</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -43976,6 +46051,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929613</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -44092,6 +46172,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103235929</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -44203,6 +46288,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117954788</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -44309,6 +46399,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929630</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -44415,6 +46510,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100936943</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -44525,6 +46625,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101291360</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -44635,6 +46740,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029360</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -44760,6 +46870,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/252540</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -44880,6 +46995,11 @@
       <c r="AY424" t="inlineStr">
         <is>
           <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/252544</t>
         </is>
       </c>
     </row>
@@ -44983,6 +47103,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132275355</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -45084,6 +47209,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133029524</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -45190,6 +47320,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004843</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -45291,6 +47426,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101291417</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -45392,6 +47532,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004867</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -45493,6 +47638,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132275368</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -45616,6 +47766,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100842766</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -45717,6 +47872,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129135141</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -45835,6 +47995,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95163424</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -45946,6 +48111,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111620333</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -46048,6 +48218,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92948043</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -46155,6 +48330,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110144345</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -46262,6 +48442,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132275412</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -46364,6 +48549,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180270</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -46466,6 +48656,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92910640</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -46568,6 +48763,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97593391</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -46674,6 +48874,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283702</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -46775,6 +48980,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175648</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -46876,6 +49086,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175654</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -46982,6 +49197,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175674</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -47083,6 +49303,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101687</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -47184,6 +49409,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664855</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -47290,6 +49520,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175907</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -47391,6 +49626,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175920</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -47492,6 +49732,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946889</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -47593,6 +49838,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624516</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -47694,6 +49944,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687156</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -47795,6 +50050,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120687284</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -47896,6 +50156,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664220</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -48001,6 +50266,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624534</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -48119,6 +50389,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99409339</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -48224,6 +50499,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129102307</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -48329,6 +50609,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175937</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -48430,6 +50715,11 @@
         </is>
       </c>
       <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175699</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -48531,6 +50821,11 @@
         </is>
       </c>
       <c r="AY459" t="inlineStr"/>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624483</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -48642,6 +50937,11 @@
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120221</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -48757,6 +51057,11 @@
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100937688</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -48867,6 +51172,11 @@
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100937744</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -48973,6 +51283,11 @@
         </is>
       </c>
       <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1439398</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -49092,6 +51407,11 @@
         </is>
       </c>
       <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106917680</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -49203,6 +51523,11 @@
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126754217</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -49310,6 +51635,11 @@
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101340988</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -49411,6 +51741,11 @@
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664081</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -49512,6 +51847,11 @@
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664114</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -49613,6 +51953,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664153</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -49714,6 +52059,11 @@
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664174</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -49819,6 +52169,11 @@
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625750</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -49924,6 +52279,11 @@
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625846</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -50029,6 +52389,11 @@
         </is>
       </c>
       <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625874</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -50134,6 +52499,11 @@
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625971</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -50235,6 +52605,11 @@
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664181</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -50340,6 +52715,11 @@
         </is>
       </c>
       <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625646</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -50445,6 +52825,11 @@
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625939</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -50546,6 +52931,11 @@
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625895</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -50647,6 +53037,11 @@
         </is>
       </c>
       <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626214</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -50748,6 +53143,11 @@
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624574</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -50849,6 +53249,11 @@
         </is>
       </c>
       <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101715</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -50950,6 +53355,11 @@
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129101739</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -51067,6 +53477,11 @@
         </is>
       </c>
       <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99410272</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -51168,6 +53583,11 @@
         </is>
       </c>
       <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97606519</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -51285,6 +53705,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99410575</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -51386,6 +53811,11 @@
         </is>
       </c>
       <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113157581</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -51487,6 +53917,11 @@
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625902</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -51588,6 +54023,11 @@
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626027</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -51689,6 +54129,11 @@
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624688</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -51790,6 +54235,11 @@
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625957</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -51891,6 +54341,11 @@
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625723</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -51992,6 +54447,11 @@
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664089</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -52093,6 +54553,11 @@
         </is>
       </c>
       <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664102</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -52198,6 +54663,11 @@
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128625919</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -52310,6 +54780,11 @@
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272871</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -52426,6 +54901,11 @@
         </is>
       </c>
       <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132677217</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -52531,6 +55011,11 @@
         </is>
       </c>
       <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626190</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -52641,6 +55126,11 @@
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99410343</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -52742,6 +55232,11 @@
         </is>
       </c>
       <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664066</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -52843,6 +55338,11 @@
         </is>
       </c>
       <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664051</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -52948,6 +55448,11 @@
         </is>
       </c>
       <c r="AY501" t="inlineStr"/>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119941575</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -53049,6 +55554,11 @@
         </is>
       </c>
       <c r="AY502" t="inlineStr"/>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626177</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -53150,6 +55660,11 @@
         </is>
       </c>
       <c r="AY503" t="inlineStr"/>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624254</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -53251,6 +55766,11 @@
         </is>
       </c>
       <c r="AY504" t="inlineStr"/>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624274</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -53352,6 +55872,11 @@
         </is>
       </c>
       <c r="AY505" t="inlineStr"/>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112664178</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -53457,6 +55982,11 @@
         </is>
       </c>
       <c r="AY506" t="inlineStr"/>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624262</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -53571,6 +56101,11 @@
         </is>
       </c>
       <c r="AY507" t="inlineStr"/>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99417820</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -53685,6 +56220,11 @@
         </is>
       </c>
       <c r="AY508" t="inlineStr"/>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99417773</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -53790,6 +56330,11 @@
         </is>
       </c>
       <c r="AY509" t="inlineStr"/>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624289</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -53906,6 +56451,11 @@
         </is>
       </c>
       <c r="AY510" t="inlineStr"/>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132675007</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -54011,6 +56561,11 @@
         </is>
       </c>
       <c r="AY511" t="inlineStr"/>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134282180</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -54131,6 +56686,11 @@
         </is>
       </c>
       <c r="AY512" t="inlineStr"/>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99418537</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -54232,6 +56792,11 @@
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98988606</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -54342,6 +56907,11 @@
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99215996</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -54443,6 +57013,11 @@
         </is>
       </c>
       <c r="AY515" t="inlineStr"/>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624244</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -54544,6 +57119,11 @@
         </is>
       </c>
       <c r="AY516" t="inlineStr"/>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97606593</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -54650,6 +57230,11 @@
         </is>
       </c>
       <c r="AY517" t="inlineStr"/>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119941561</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -54751,6 +57336,11 @@
         </is>
       </c>
       <c r="AY518" t="inlineStr"/>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624249</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -54861,6 +57451,11 @@
         </is>
       </c>
       <c r="AY519" t="inlineStr"/>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128624193</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -54968,6 +57563,11 @@
         </is>
       </c>
       <c r="AY520" t="inlineStr"/>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117893184</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -55074,6 +57674,11 @@
         </is>
       </c>
       <c r="AY521" t="inlineStr"/>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90397833</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -55175,6 +57780,11 @@
         </is>
       </c>
       <c r="AY522" t="inlineStr"/>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97350909</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -55291,6 +57901,11 @@
         </is>
       </c>
       <c r="AY523" t="inlineStr"/>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132675032</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -55397,6 +58012,11 @@
         </is>
       </c>
       <c r="AY524" t="inlineStr"/>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92085944</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -55503,6 +58123,11 @@
         </is>
       </c>
       <c r="AY525" t="inlineStr"/>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128545693</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -55604,6 +58229,11 @@
         </is>
       </c>
       <c r="AY526" t="inlineStr"/>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112665120</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -55705,6 +58335,11 @@
         </is>
       </c>
       <c r="AY527" t="inlineStr"/>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122756287</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -55811,6 +58446,11 @@
         </is>
       </c>
       <c r="AY528" t="inlineStr"/>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131822233</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -55916,6 +58556,11 @@
         </is>
       </c>
       <c r="AY529" t="inlineStr"/>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132511008</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -56017,6 +58662,11 @@
         </is>
       </c>
       <c r="AY530" t="inlineStr"/>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114826454</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -56122,6 +58772,11 @@
         </is>
       </c>
       <c r="AY531" t="inlineStr"/>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121424387</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -56236,6 +58891,11 @@
         </is>
       </c>
       <c r="AY532" t="inlineStr"/>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105650122</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -56343,6 +59003,11 @@
         </is>
       </c>
       <c r="AY533" t="inlineStr"/>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105650118</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -56445,6 +59110,11 @@
         </is>
       </c>
       <c r="AY534" t="inlineStr"/>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91923359</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -56556,8 +59226,549 @@
         </is>
       </c>
       <c r="AY535" t="inlineStr"/>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105650113</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -17613,7 +17613,7 @@
         <v>135387324</v>
       </c>
       <c r="B158" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>135387419</v>
       </c>
       <c r="B225" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         <v>134928880</v>
       </c>
       <c r="B260" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -38317,7 +38317,7 @@
         <v>134929749</v>
       </c>
       <c r="B347" t="n">
-        <v>57776</v>
+        <v>57781</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>134929407</v>
       </c>
       <c r="B356" t="n">
-        <v>96629</v>
+        <v>96673</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>135387367</v>
       </c>
       <c r="B391" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>134929613</v>
       </c>
       <c r="B416" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>134929630</v>
       </c>
       <c r="B419" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -24852,7 +24852,7 @@
         <v>135387419</v>
       </c>
       <c r="B225" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -24969,7 +24969,7 @@
         <v>135387419</v>
       </c>
       <c r="B226" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -42333,7 +42333,7 @@
         <v>129134736</v>
       </c>
       <c r="B383" t="n">
-        <v>93215</v>
+        <v>93365</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -6963,7 +6963,7 @@
         <v>135827391</v>
       </c>
       <c r="B60" t="n">
-        <v>56930</v>
+        <v>56932</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135970465</v>
       </c>
       <c r="B160" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>135970367</v>
       </c>
       <c r="B242" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106432</v>
+        <v>106433</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>135970485</v>
       </c>
       <c r="B289" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93343</v>
+        <v>93358</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93365</v>
+        <v>93380</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93358</v>
+        <v>93359</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93380</v>
+        <v>93381</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93359</v>
+        <v>93360</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93381</v>
+        <v>93382</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -6963,7 +6963,7 @@
         <v>135827391</v>
       </c>
       <c r="B60" t="n">
-        <v>56932</v>
+        <v>56933</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135970465</v>
       </c>
       <c r="B160" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>135970367</v>
       </c>
       <c r="B242" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>136050518</v>
       </c>
       <c r="B250" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>135970485</v>
       </c>
       <c r="B289" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93360</v>
+        <v>93361</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>136050600</v>
       </c>
       <c r="B347" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93382</v>
+        <v>93383</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -6963,7 +6963,7 @@
         <v>135827391</v>
       </c>
       <c r="B60" t="n">
-        <v>56933</v>
+        <v>56937</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135970465</v>
       </c>
       <c r="B160" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>135970367</v>
       </c>
       <c r="B242" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>136050518</v>
       </c>
       <c r="B250" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>135970485</v>
       </c>
       <c r="B289" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93361</v>
+        <v>93367</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>136050600</v>
       </c>
       <c r="B347" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93383</v>
+        <v>93389</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -6963,7 +6963,7 @@
         <v>135827391</v>
       </c>
       <c r="B60" t="n">
-        <v>56937</v>
+        <v>56938</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135970465</v>
       </c>
       <c r="B160" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>135970367</v>
       </c>
       <c r="B242" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>136050518</v>
       </c>
       <c r="B250" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>135970485</v>
       </c>
       <c r="B289" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>136050600</v>
       </c>
       <c r="B347" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93368</v>
+        <v>93374</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>

--- a/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
+++ b/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx
@@ -6963,7 +6963,7 @@
         <v>135827391</v>
       </c>
       <c r="B60" t="n">
-        <v>56938</v>
+        <v>56943</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>135970465</v>
       </c>
       <c r="B160" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -25079,7 +25079,7 @@
         <v>135387419</v>
       </c>
       <c r="B227" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>135970367</v>
       </c>
       <c r="B242" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>136050518</v>
       </c>
       <c r="B250" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>136050490</v>
       </c>
       <c r="B252" t="n">
-        <v>106455</v>
+        <v>106468</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31868,7 +31868,7 @@
         <v>135970485</v>
       </c>
       <c r="B289" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>135991610</v>
       </c>
       <c r="B302" t="n">
-        <v>93374</v>
+        <v>93381</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>136050600</v>
       </c>
       <c r="B347" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>129134736</v>
       </c>
       <c r="B386" t="n">
-        <v>93396</v>
+        <v>93403</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
